--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD537"/>
+  <dimension ref="A1:AD546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13759,10 +13759,10 @@
         <v>275634.73</v>
       </c>
       <c r="R147" t="n">
-        <v>228162.34</v>
+        <v>259264.94</v>
       </c>
       <c r="S147" t="n">
-        <v>192112.68</v>
+        <v>218301.07</v>
       </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
@@ -13781,7 +13781,7 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="n">
-        <v>192112.68</v>
+        <v>218301.07</v>
       </c>
     </row>
     <row r="148">
@@ -13947,10 +13947,10 @@
         <v>75000.00999999999</v>
       </c>
       <c r="R149" t="n">
-        <v>60353.76</v>
+        <v>67986.2</v>
       </c>
       <c r="S149" t="n">
-        <v>55191.63</v>
+        <v>59669.38</v>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
@@ -13969,7 +13969,7 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr"/>
       <c r="AD149" t="n">
-        <v>55191.63</v>
+        <v>59669.38</v>
       </c>
     </row>
     <row r="150">
@@ -14041,7 +14041,7 @@
         <v>679741.3199999999</v>
       </c>
       <c r="R150" t="n">
-        <v>532088</v>
+        <v>616358.11</v>
       </c>
       <c r="S150" t="n">
         <v>443139.67</v>
@@ -14135,7 +14135,7 @@
         <v>2057254.45</v>
       </c>
       <c r="R151" t="n">
-        <v>1653787.16</v>
+        <v>1971922.91</v>
       </c>
       <c r="S151" t="n">
         <v>1382564.38</v>
@@ -14229,10 +14229,10 @@
         <v>139802.65</v>
       </c>
       <c r="R152" t="n">
-        <v>103830.02</v>
+        <v>128139.94</v>
       </c>
       <c r="S152" t="n">
-        <v>96683.03</v>
+        <v>115433.55</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
@@ -14251,7 +14251,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="n">
-        <v>96683.03</v>
+        <v>115433.55</v>
       </c>
     </row>
     <row r="153">
@@ -14323,10 +14323,10 @@
         <v>15560.85</v>
       </c>
       <c r="R153" t="n">
-        <v>12100.13</v>
+        <v>14317.01</v>
       </c>
       <c r="S153" t="n">
-        <v>11606.52</v>
+        <v>13716.99</v>
       </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
@@ -14345,7 +14345,7 @@
       <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="n">
-        <v>11606.52</v>
+        <v>13716.99</v>
       </c>
     </row>
     <row r="154">
@@ -14417,10 +14417,10 @@
         <v>460199.37</v>
       </c>
       <c r="R154" t="n">
-        <v>351702.49</v>
+        <v>413076.37</v>
       </c>
       <c r="S154" t="n">
-        <v>253485.17</v>
+        <v>305161.97</v>
       </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
@@ -14439,7 +14439,7 @@
       <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr"/>
       <c r="AD154" t="n">
-        <v>253485.17</v>
+        <v>305161.97</v>
       </c>
     </row>
     <row r="155">
@@ -14514,7 +14514,7 @@
         <v>9732274.390000001</v>
       </c>
       <c r="S155" t="n">
-        <v>6371449.66</v>
+        <v>9615487.119999999</v>
       </c>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
@@ -14533,7 +14533,7 @@
       <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="inlineStr"/>
       <c r="AD155" t="n">
-        <v>6371449.66</v>
+        <v>9615487.119999999</v>
       </c>
     </row>
     <row r="156">
@@ -14602,10 +14602,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>73900</v>
+        <v>73687.2</v>
       </c>
       <c r="R156" t="n">
-        <v>41633.27</v>
+        <v>41420.47</v>
       </c>
       <c r="S156" t="n">
         <v>42733.27</v>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="n">
-        <v>73900</v>
+        <v>73687.2</v>
       </c>
       <c r="AA156" t="inlineStr"/>
       <c r="AB156" t="inlineStr"/>
@@ -16292,7 +16292,7 @@
         <v>35809.68</v>
       </c>
       <c r="S174" t="n">
-        <v>29332.76</v>
+        <v>35165.15</v>
       </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
@@ -16311,7 +16311,7 @@
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr"/>
       <c r="AD174" t="n">
-        <v>29332.76</v>
+        <v>35165.15</v>
       </c>
     </row>
     <row r="175">
@@ -16386,7 +16386,7 @@
         <v>15155.12</v>
       </c>
       <c r="S175" t="n">
-        <v>10868.92</v>
+        <v>14568.07</v>
       </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr"/>
       <c r="AD175" t="n">
-        <v>10868.92</v>
+        <v>14568.07</v>
       </c>
     </row>
     <row r="176">
@@ -16480,7 +16480,7 @@
         <v>111539.87</v>
       </c>
       <c r="S176" t="n">
-        <v>75680.95</v>
+        <v>104558.43</v>
       </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
@@ -16499,7 +16499,7 @@
       <c r="AB176" t="inlineStr"/>
       <c r="AC176" t="inlineStr"/>
       <c r="AD176" t="n">
-        <v>75680.95</v>
+        <v>104558.43</v>
       </c>
     </row>
     <row r="177">
@@ -16574,7 +16574,7 @@
         <v>86942.81</v>
       </c>
       <c r="S177" t="n">
-        <v>65605.03999999999</v>
+        <v>82642.63</v>
       </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
@@ -16593,7 +16593,7 @@
       <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="n">
-        <v>65605.03999999999</v>
+        <v>82642.63</v>
       </c>
     </row>
     <row r="178">
@@ -16668,7 +16668,7 @@
         <v>40443.58</v>
       </c>
       <c r="S178" t="n">
-        <v>31263.08</v>
+        <v>40109.77</v>
       </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
@@ -16687,7 +16687,7 @@
       <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="inlineStr"/>
       <c r="AD178" t="n">
-        <v>31263.08</v>
+        <v>40109.77</v>
       </c>
     </row>
     <row r="179">
@@ -16762,7 +16762,7 @@
         <v>9343.91</v>
       </c>
       <c r="S179" t="n">
-        <v>8235.469999999999</v>
+        <v>9343.91</v>
       </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
@@ -16781,7 +16781,7 @@
       <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="inlineStr"/>
       <c r="AD179" t="n">
-        <v>8235.469999999999</v>
+        <v>9343.91</v>
       </c>
     </row>
     <row r="180">
@@ -17138,7 +17138,7 @@
         <v>876886.59</v>
       </c>
       <c r="S183" t="n">
-        <v>616245.1800000001</v>
+        <v>731114.9</v>
       </c>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
@@ -17157,7 +17157,7 @@
       <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="inlineStr"/>
       <c r="AD183" t="n">
-        <v>616245.1800000001</v>
+        <v>731114.9</v>
       </c>
     </row>
     <row r="184">
@@ -17232,7 +17232,7 @@
         <v>500753.65</v>
       </c>
       <c r="S184" t="n">
-        <v>376803.3</v>
+        <v>445670.74</v>
       </c>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
@@ -17251,7 +17251,7 @@
       <c r="AB184" t="inlineStr"/>
       <c r="AC184" t="inlineStr"/>
       <c r="AD184" t="n">
-        <v>376803.3</v>
+        <v>445670.74</v>
       </c>
     </row>
     <row r="185">
@@ -17326,7 +17326,7 @@
         <v>1977389.7</v>
       </c>
       <c r="S185" t="n">
-        <v>1446217.81</v>
+        <v>1642404.45</v>
       </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="inlineStr"/>
       <c r="AD185" t="n">
-        <v>1446217.81</v>
+        <v>1642404.45</v>
       </c>
     </row>
     <row r="186">
@@ -17420,7 +17420,7 @@
         <v>1884588.14</v>
       </c>
       <c r="S186" t="n">
-        <v>1285107.36</v>
+        <v>1574300.56</v>
       </c>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
@@ -17439,7 +17439,7 @@
       <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr"/>
       <c r="AD186" t="n">
-        <v>1285107.36</v>
+        <v>1574300.56</v>
       </c>
     </row>
     <row r="187">
@@ -17514,7 +17514,7 @@
         <v>1415678.48</v>
       </c>
       <c r="S187" t="n">
-        <v>988621.6899999999</v>
+        <v>1209897.74</v>
       </c>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
@@ -17533,7 +17533,7 @@
       <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="n">
-        <v>988621.6899999999</v>
+        <v>1209897.74</v>
       </c>
     </row>
     <row r="188">
@@ -17608,7 +17608,7 @@
         <v>347013.97</v>
       </c>
       <c r="S188" t="n">
-        <v>270289.53</v>
+        <v>308842.43</v>
       </c>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
@@ -17627,7 +17627,7 @@
       <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="inlineStr"/>
       <c r="AD188" t="n">
-        <v>270289.53</v>
+        <v>308842.43</v>
       </c>
     </row>
     <row r="189">
@@ -17702,7 +17702,7 @@
         <v>42713.34</v>
       </c>
       <c r="S189" t="n">
-        <v>41553.09</v>
+        <v>41681.03</v>
       </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
@@ -17721,7 +17721,7 @@
       <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr"/>
       <c r="AD189" t="n">
-        <v>41553.09</v>
+        <v>41681.03</v>
       </c>
     </row>
     <row r="190">
@@ -18450,7 +18450,7 @@
         <v>2855.69</v>
       </c>
       <c r="S197" t="n">
-        <v>2301.47</v>
+        <v>2855.69</v>
       </c>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
@@ -18469,7 +18469,7 @@
       <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="n">
-        <v>2301.47</v>
+        <v>2855.69</v>
       </c>
     </row>
     <row r="198">
@@ -18544,7 +18544,7 @@
         <v>111881.12</v>
       </c>
       <c r="S198" t="n">
-        <v>80402.44</v>
+        <v>99574.19</v>
       </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
@@ -18563,7 +18563,7 @@
       <c r="AB198" t="inlineStr"/>
       <c r="AC198" t="inlineStr"/>
       <c r="AD198" t="n">
-        <v>80402.44</v>
+        <v>99574.19</v>
       </c>
     </row>
     <row r="199">
@@ -20315,7 +20315,7 @@
         <v>256779</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>173979</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -20409,10 +20409,10 @@
         <v>267582.82</v>
       </c>
       <c r="R218" t="n">
-        <v>211991.51</v>
+        <v>267582.82</v>
       </c>
       <c r="S218" t="n">
-        <v>211991.51</v>
+        <v>267582.82</v>
       </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
@@ -20431,7 +20431,7 @@
       <c r="AB218" t="inlineStr"/>
       <c r="AC218" t="inlineStr"/>
       <c r="AD218" t="n">
-        <v>211991.51</v>
+        <v>267582.82</v>
       </c>
     </row>
     <row r="219">
@@ -20597,7 +20597,7 @@
         <v>6977375.41</v>
       </c>
       <c r="R220" t="n">
-        <v>868789.0600000001</v>
+        <v>3356349.34</v>
       </c>
       <c r="S220" t="n">
         <v>858363.6</v>
@@ -20694,7 +20694,7 @@
         <v>3356349.34</v>
       </c>
       <c r="S221" t="n">
-        <v>858363.59</v>
+        <v>3316073.15</v>
       </c>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
@@ -20713,7 +20713,7 @@
       <c r="AB221" t="inlineStr"/>
       <c r="AC221" t="inlineStr"/>
       <c r="AD221" t="n">
-        <v>858363.59</v>
+        <v>3316073.15</v>
       </c>
     </row>
     <row r="222">
@@ -36766,7 +36766,7 @@
         <v>8789.42</v>
       </c>
       <c r="S399" t="n">
-        <v>4987.97</v>
+        <v>8554.15</v>
       </c>
       <c r="T399" t="inlineStr"/>
       <c r="U399" t="inlineStr"/>
@@ -36785,7 +36785,7 @@
       <c r="AB399" t="inlineStr"/>
       <c r="AC399" t="inlineStr"/>
       <c r="AD399" t="n">
-        <v>4987.97</v>
+        <v>8554.15</v>
       </c>
     </row>
     <row r="400">
@@ -36860,7 +36860,7 @@
         <v>252529.96</v>
       </c>
       <c r="S400" t="n">
-        <v>166894.69</v>
+        <v>224751.67</v>
       </c>
       <c r="T400" t="inlineStr"/>
       <c r="U400" t="inlineStr"/>
@@ -36879,7 +36879,7 @@
       <c r="AB400" t="inlineStr"/>
       <c r="AC400" t="inlineStr"/>
       <c r="AD400" t="n">
-        <v>166894.69</v>
+        <v>224751.67</v>
       </c>
     </row>
     <row r="401">
@@ -36954,7 +36954,7 @@
         <v>39114.47</v>
       </c>
       <c r="S401" t="n">
-        <v>34514.98</v>
+        <v>35471.93</v>
       </c>
       <c r="T401" t="inlineStr"/>
       <c r="U401" t="inlineStr"/>
@@ -36973,7 +36973,7 @@
       <c r="AB401" t="inlineStr"/>
       <c r="AC401" t="inlineStr"/>
       <c r="AD401" t="n">
-        <v>34514.98</v>
+        <v>35471.93</v>
       </c>
     </row>
     <row r="402">
@@ -37048,7 +37048,7 @@
         <v>21214.4</v>
       </c>
       <c r="S402" t="n">
-        <v>18811.66</v>
+        <v>19003.05</v>
       </c>
       <c r="T402" t="inlineStr"/>
       <c r="U402" t="inlineStr"/>
@@ -37067,7 +37067,7 @@
       <c r="AB402" t="inlineStr"/>
       <c r="AC402" t="inlineStr"/>
       <c r="AD402" t="n">
-        <v>18811.66</v>
+        <v>19003.05</v>
       </c>
     </row>
     <row r="403">
@@ -37142,7 +37142,7 @@
         <v>87506.44</v>
       </c>
       <c r="S403" t="n">
-        <v>33987.97</v>
+        <v>35710.48</v>
       </c>
       <c r="T403" t="inlineStr"/>
       <c r="U403" t="inlineStr"/>
@@ -37161,7 +37161,7 @@
       <c r="AB403" t="inlineStr"/>
       <c r="AC403" t="inlineStr"/>
       <c r="AD403" t="n">
-        <v>33987.97</v>
+        <v>35710.48</v>
       </c>
     </row>
     <row r="404">
@@ -37236,7 +37236,7 @@
         <v>86503.2</v>
       </c>
       <c r="S404" t="n">
-        <v>50862.48</v>
+        <v>52687.06</v>
       </c>
       <c r="T404" t="inlineStr"/>
       <c r="U404" t="inlineStr"/>
@@ -37255,7 +37255,7 @@
       <c r="AB404" t="inlineStr"/>
       <c r="AC404" t="inlineStr"/>
       <c r="AD404" t="n">
-        <v>50862.48</v>
+        <v>52687.06</v>
       </c>
     </row>
     <row r="405">
@@ -37330,7 +37330,7 @@
         <v>62694</v>
       </c>
       <c r="S405" t="n">
-        <v>55456.22</v>
+        <v>56706.63</v>
       </c>
       <c r="T405" t="inlineStr"/>
       <c r="U405" t="inlineStr"/>
@@ -37349,7 +37349,7 @@
       <c r="AB405" t="inlineStr"/>
       <c r="AC405" t="inlineStr"/>
       <c r="AD405" t="n">
-        <v>55456.22</v>
+        <v>56706.63</v>
       </c>
     </row>
     <row r="406">
@@ -37424,7 +37424,7 @@
         <v>14763.95</v>
       </c>
       <c r="S406" t="n">
-        <v>12980.4</v>
+        <v>13452.49</v>
       </c>
       <c r="T406" t="inlineStr"/>
       <c r="U406" t="inlineStr"/>
@@ -37443,7 +37443,7 @@
       <c r="AB406" t="inlineStr"/>
       <c r="AC406" t="inlineStr"/>
       <c r="AD406" t="n">
-        <v>12980.4</v>
+        <v>13452.49</v>
       </c>
     </row>
     <row r="407">
@@ -37518,7 +37518,7 @@
         <v>3723.84</v>
       </c>
       <c r="S407" t="n">
-        <v>3240.1</v>
+        <v>3393.21</v>
       </c>
       <c r="T407" t="inlineStr"/>
       <c r="U407" t="inlineStr"/>
@@ -37537,7 +37537,7 @@
       <c r="AB407" t="inlineStr"/>
       <c r="AC407" t="inlineStr"/>
       <c r="AD407" t="n">
-        <v>3240.1</v>
+        <v>3393.21</v>
       </c>
     </row>
     <row r="408">
@@ -37609,10 +37609,10 @@
         <v>109845.87</v>
       </c>
       <c r="R408" t="n">
-        <v>81568.64999999999</v>
+        <v>109845.87</v>
       </c>
       <c r="S408" t="n">
-        <v>81568.64999999999</v>
+        <v>109845.87</v>
       </c>
       <c r="T408" t="inlineStr"/>
       <c r="U408" t="inlineStr"/>
@@ -37627,7 +37627,7 @@
       <c r="AB408" t="inlineStr"/>
       <c r="AC408" t="inlineStr"/>
       <c r="AD408" t="n">
-        <v>81568.64999999999</v>
+        <v>109845.87</v>
       </c>
     </row>
     <row r="409">
@@ -38059,10 +38059,10 @@
         <v>12892.12</v>
       </c>
       <c r="R413" t="n">
-        <v>10857.68</v>
+        <v>11623.24</v>
       </c>
       <c r="S413" t="n">
-        <v>8015.6</v>
+        <v>8744.41</v>
       </c>
       <c r="T413" t="inlineStr"/>
       <c r="U413" t="inlineStr"/>
@@ -38081,7 +38081,7 @@
       <c r="AB413" t="inlineStr"/>
       <c r="AC413" t="inlineStr"/>
       <c r="AD413" t="n">
-        <v>8015.6</v>
+        <v>8744.41</v>
       </c>
     </row>
     <row r="414">
@@ -38153,10 +38153,10 @@
         <v>34485.5</v>
       </c>
       <c r="R414" t="n">
-        <v>32789.49</v>
+        <v>33542.29</v>
       </c>
       <c r="S414" t="n">
-        <v>24851.84</v>
+        <v>25568.51</v>
       </c>
       <c r="T414" t="inlineStr"/>
       <c r="U414" t="inlineStr"/>
@@ -38175,7 +38175,7 @@
       <c r="AB414" t="inlineStr"/>
       <c r="AC414" t="inlineStr"/>
       <c r="AD414" t="n">
-        <v>24851.84</v>
+        <v>25568.51</v>
       </c>
     </row>
     <row r="415">
@@ -38247,10 +38247,10 @@
         <v>89169.53</v>
       </c>
       <c r="R415" t="n">
-        <v>85680.89</v>
+        <v>88251.88</v>
       </c>
       <c r="S415" t="n">
-        <v>63507.86</v>
+        <v>65955.44</v>
       </c>
       <c r="T415" t="inlineStr"/>
       <c r="U415" t="inlineStr"/>
@@ -38269,7 +38269,7 @@
       <c r="AB415" t="inlineStr"/>
       <c r="AC415" t="inlineStr"/>
       <c r="AD415" t="n">
-        <v>63507.86</v>
+        <v>65955.44</v>
       </c>
     </row>
     <row r="416">
@@ -38438,7 +38438,7 @@
         <v>28315.64</v>
       </c>
       <c r="S417" t="n">
-        <v>13617.87</v>
+        <v>27975.85</v>
       </c>
       <c r="T417" t="inlineStr"/>
       <c r="U417" t="inlineStr"/>
@@ -38457,7 +38457,7 @@
       <c r="AB417" t="inlineStr"/>
       <c r="AC417" t="inlineStr"/>
       <c r="AD417" t="n">
-        <v>13617.87</v>
+        <v>27975.85</v>
       </c>
     </row>
     <row r="418">
@@ -38620,7 +38620,7 @@
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>46966.74</v>
+        <v>58944.84</v>
       </c>
       <c r="R419" t="n">
         <v>46966.74</v>
@@ -38635,7 +38635,7 @@
       <c r="X419" t="inlineStr"/>
       <c r="Y419" t="inlineStr"/>
       <c r="Z419" t="n">
-        <v>46966.74</v>
+        <v>58944.84</v>
       </c>
       <c r="AA419" t="inlineStr"/>
       <c r="AB419" t="inlineStr"/>
@@ -38710,7 +38710,7 @@
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>2487.09</v>
+        <v>3232.69</v>
       </c>
       <c r="R420" t="n">
         <v>2487.09</v>
@@ -38725,7 +38725,7 @@
       <c r="X420" t="inlineStr"/>
       <c r="Y420" t="inlineStr"/>
       <c r="Z420" t="n">
-        <v>2487.09</v>
+        <v>3232.69</v>
       </c>
       <c r="AA420" t="inlineStr"/>
       <c r="AB420" t="inlineStr"/>
@@ -38800,7 +38800,7 @@
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>83312.7</v>
+        <v>111083.6</v>
       </c>
       <c r="R421" t="n">
         <v>83312.7</v>
@@ -38815,7 +38815,7 @@
       <c r="X421" t="inlineStr"/>
       <c r="Y421" t="inlineStr"/>
       <c r="Z421" t="n">
-        <v>83312.7</v>
+        <v>111083.6</v>
       </c>
       <c r="AA421" t="inlineStr"/>
       <c r="AB421" t="inlineStr"/>
@@ -38890,7 +38890,7 @@
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>190387.12</v>
+        <v>258868.99</v>
       </c>
       <c r="R422" t="n">
         <v>190387.12</v>
@@ -38905,7 +38905,7 @@
       <c r="X422" t="inlineStr"/>
       <c r="Y422" t="inlineStr"/>
       <c r="Z422" t="n">
-        <v>190387.12</v>
+        <v>258868.99</v>
       </c>
       <c r="AA422" t="inlineStr"/>
       <c r="AB422" t="inlineStr"/>
@@ -39250,7 +39250,7 @@
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>1541.63</v>
+        <v>2055.17</v>
       </c>
       <c r="R426" t="n">
         <v>1540.63</v>
@@ -39265,7 +39265,7 @@
       <c r="X426" t="inlineStr"/>
       <c r="Y426" t="inlineStr"/>
       <c r="Z426" t="n">
-        <v>1541.63</v>
+        <v>2055.17</v>
       </c>
       <c r="AA426" t="inlineStr"/>
       <c r="AB426" t="inlineStr"/>
@@ -39340,7 +39340,7 @@
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>10063.48</v>
+        <v>13812.6</v>
       </c>
       <c r="R427" t="n">
         <v>10063.48</v>
@@ -39355,7 +39355,7 @@
       <c r="X427" t="inlineStr"/>
       <c r="Y427" t="inlineStr"/>
       <c r="Z427" t="n">
-        <v>10063.48</v>
+        <v>13812.6</v>
       </c>
       <c r="AA427" t="inlineStr"/>
       <c r="AB427" t="inlineStr"/>
@@ -39994,7 +39994,7 @@
         </is>
       </c>
       <c r="Q434" t="n">
-        <v>2619.57</v>
+        <v>3365.18</v>
       </c>
       <c r="R434" t="n">
         <v>2619.57</v>
@@ -40013,7 +40013,7 @@
       </c>
       <c r="Y434" t="inlineStr"/>
       <c r="Z434" t="n">
-        <v>2619.57</v>
+        <v>3365.18</v>
       </c>
       <c r="AA434" t="inlineStr"/>
       <c r="AB434" t="inlineStr"/>
@@ -40370,7 +40370,7 @@
         </is>
       </c>
       <c r="Q438" t="n">
-        <v>147328.11</v>
+        <v>196437.48</v>
       </c>
       <c r="R438" t="n">
         <v>147328.11</v>
@@ -40389,7 +40389,7 @@
       </c>
       <c r="Y438" t="inlineStr"/>
       <c r="Z438" t="n">
-        <v>147328.11</v>
+        <v>196437.48</v>
       </c>
       <c r="AA438" t="inlineStr"/>
       <c r="AB438" t="inlineStr"/>
@@ -40464,7 +40464,7 @@
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>49109.37</v>
+        <v>65479.16</v>
       </c>
       <c r="R439" t="n">
         <v>49109.37</v>
@@ -40483,7 +40483,7 @@
       </c>
       <c r="Y439" t="inlineStr"/>
       <c r="Z439" t="n">
-        <v>49109.37</v>
+        <v>65479.16</v>
       </c>
       <c r="AA439" t="inlineStr"/>
       <c r="AB439" t="inlineStr"/>
@@ -41028,7 +41028,7 @@
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>7809.61</v>
+        <v>10046.44</v>
       </c>
       <c r="R445" t="n">
         <v>7809.61</v>
@@ -41047,7 +41047,7 @@
       </c>
       <c r="Y445" t="inlineStr"/>
       <c r="Z445" t="n">
-        <v>7809.61</v>
+        <v>10046.44</v>
       </c>
       <c r="AA445" t="inlineStr"/>
       <c r="AB445" t="inlineStr"/>
@@ -41122,7 +41122,7 @@
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>5239.14</v>
+        <v>6756.75</v>
       </c>
       <c r="R446" t="n">
         <v>5239.14</v>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="Y446" t="inlineStr"/>
       <c r="Z446" t="n">
-        <v>5239.14</v>
+        <v>6756.75</v>
       </c>
       <c r="AA446" t="inlineStr"/>
       <c r="AB446" t="inlineStr"/>
@@ -41216,7 +41216,7 @@
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>98218.74000000001</v>
+        <v>130958.32</v>
       </c>
       <c r="R447" t="n">
         <v>98218.74000000001</v>
@@ -41235,7 +41235,7 @@
       </c>
       <c r="Y447" t="inlineStr"/>
       <c r="Z447" t="n">
-        <v>98218.74000000001</v>
+        <v>130958.32</v>
       </c>
       <c r="AA447" t="inlineStr"/>
       <c r="AB447" t="inlineStr"/>
@@ -41496,7 +41496,7 @@
         <v>217771.81</v>
       </c>
       <c r="S450" t="n">
-        <v>0</v>
+        <v>215158.55</v>
       </c>
       <c r="T450" t="inlineStr"/>
       <c r="U450" t="inlineStr"/>
@@ -41515,7 +41515,7 @@
       <c r="AB450" t="inlineStr"/>
       <c r="AC450" t="inlineStr"/>
       <c r="AD450" t="n">
-        <v>0</v>
+        <v>215158.55</v>
       </c>
     </row>
     <row r="451">
@@ -41864,7 +41864,7 @@
         <v>85.45999999999999</v>
       </c>
       <c r="S454" t="n">
-        <v>0</v>
+        <v>84.44</v>
       </c>
       <c r="T454" t="inlineStr"/>
       <c r="U454" t="inlineStr"/>
@@ -41879,7 +41879,7 @@
       <c r="AB454" t="inlineStr"/>
       <c r="AC454" t="inlineStr"/>
       <c r="AD454" t="n">
-        <v>0</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="455">
@@ -42781,7 +42781,7 @@
         <v>2986.8</v>
       </c>
       <c r="R464" t="n">
-        <v>0</v>
+        <v>2986.8</v>
       </c>
       <c r="S464" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>94512.00999999999</v>
       </c>
       <c r="S468" t="n">
-        <v>0</v>
+        <v>94268.48</v>
       </c>
       <c r="T468" t="inlineStr"/>
       <c r="U468" t="inlineStr"/>
@@ -43171,7 +43171,7 @@
       <c r="AB468" t="inlineStr"/>
       <c r="AC468" t="inlineStr"/>
       <c r="AD468" t="n">
-        <v>0</v>
+        <v>94268.48</v>
       </c>
     </row>
     <row r="469">
@@ -43340,7 +43340,7 @@
         <v>6959.88</v>
       </c>
       <c r="S470" t="n">
-        <v>0</v>
+        <v>6959.88</v>
       </c>
       <c r="T470" t="inlineStr"/>
       <c r="U470" t="inlineStr"/>
@@ -43359,7 +43359,7 @@
       <c r="AB470" t="inlineStr"/>
       <c r="AC470" t="inlineStr"/>
       <c r="AD470" t="n">
-        <v>0</v>
+        <v>6959.88</v>
       </c>
     </row>
     <row r="471">
@@ -46155,10 +46155,10 @@
         <v>6588.2</v>
       </c>
       <c r="R501" t="n">
-        <v>5341.14</v>
+        <v>6588.19</v>
       </c>
       <c r="S501" t="n">
-        <v>4915.32</v>
+        <v>6102.51</v>
       </c>
       <c r="T501" t="inlineStr"/>
       <c r="U501" t="inlineStr"/>
@@ -46177,7 +46177,7 @@
       <c r="AB501" t="inlineStr"/>
       <c r="AC501" t="inlineStr"/>
       <c r="AD501" t="n">
-        <v>4915.32</v>
+        <v>6102.51</v>
       </c>
     </row>
     <row r="502">
@@ -46718,7 +46718,7 @@
         <v>1084.54</v>
       </c>
       <c r="S507" t="n">
-        <v>510.37</v>
+        <v>1084.54</v>
       </c>
       <c r="T507" t="inlineStr"/>
       <c r="U507" t="inlineStr"/>
@@ -46737,7 +46737,7 @@
       <c r="AB507" t="inlineStr"/>
       <c r="AC507" t="inlineStr"/>
       <c r="AD507" t="n">
-        <v>510.37</v>
+        <v>1084.54</v>
       </c>
     </row>
     <row r="508">
@@ -47737,10 +47737,10 @@
         <v>3309.12</v>
       </c>
       <c r="R518" t="n">
-        <v>1498.22</v>
+        <v>3309.12</v>
       </c>
       <c r="S518" t="n">
-        <v>1498.22</v>
+        <v>3309.12</v>
       </c>
       <c r="T518" t="inlineStr"/>
       <c r="U518" t="inlineStr"/>
@@ -47759,7 +47759,7 @@
       <c r="AB518" t="inlineStr"/>
       <c r="AC518" t="inlineStr"/>
       <c r="AD518" t="n">
-        <v>1498.22</v>
+        <v>3309.12</v>
       </c>
     </row>
     <row r="519">
@@ -48301,10 +48301,10 @@
         <v>8485.08</v>
       </c>
       <c r="R524" t="n">
-        <v>1984.05</v>
+        <v>8485.08</v>
       </c>
       <c r="S524" t="n">
-        <v>1984.05</v>
+        <v>8485.08</v>
       </c>
       <c r="T524" t="inlineStr"/>
       <c r="U524" t="inlineStr"/>
@@ -48319,7 +48319,7 @@
       <c r="AB524" t="inlineStr"/>
       <c r="AC524" t="inlineStr"/>
       <c r="AD524" t="n">
-        <v>1984.05</v>
+        <v>8485.08</v>
       </c>
     </row>
     <row r="525">
@@ -49516,6 +49516,852 @@
         <v>0</v>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B538" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C538" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>343</v>
+      </c>
+      <c r="F538" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>2301520 000010/2025</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>CONCORRENCIA - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I538" t="n">
+        <v>51</v>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K538" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M538" t="n">
+        <v>80</v>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>08.697.901/0001-96</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
+        </is>
+      </c>
+      <c r="Q538" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="R538" t="n">
+        <v>0</v>
+      </c>
+      <c r="S538" t="n">
+        <v>0</v>
+      </c>
+      <c r="T538" t="inlineStr"/>
+      <c r="U538" t="inlineStr"/>
+      <c r="V538" t="n">
+        <v>0</v>
+      </c>
+      <c r="W538" t="inlineStr"/>
+      <c r="X538" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y538" t="inlineStr"/>
+      <c r="Z538" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AA538" t="inlineStr"/>
+      <c r="AB538" t="inlineStr"/>
+      <c r="AC538" t="inlineStr"/>
+      <c r="AD538" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B539" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C539" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>344</v>
+      </c>
+      <c r="F539" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>2301520 000015/2026</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I539" t="n">
+        <v>51</v>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K539" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M539" t="n">
+        <v>80</v>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q539" t="n">
+        <v>4027233.6</v>
+      </c>
+      <c r="R539" t="n">
+        <v>0</v>
+      </c>
+      <c r="S539" t="n">
+        <v>0</v>
+      </c>
+      <c r="T539" t="inlineStr"/>
+      <c r="U539" t="inlineStr"/>
+      <c r="V539" t="n">
+        <v>0</v>
+      </c>
+      <c r="W539" t="inlineStr"/>
+      <c r="X539" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y539" t="inlineStr"/>
+      <c r="Z539" t="n">
+        <v>4027233.6</v>
+      </c>
+      <c r="AA539" t="inlineStr"/>
+      <c r="AB539" t="inlineStr"/>
+      <c r="AC539" t="inlineStr"/>
+      <c r="AD539" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B540" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C540" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>345</v>
+      </c>
+      <c r="F540" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I540" t="n">
+        <v>93</v>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K540" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M540" t="n">
+        <v>80</v>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q540" t="n">
+        <v>250000</v>
+      </c>
+      <c r="R540" t="n">
+        <v>0</v>
+      </c>
+      <c r="S540" t="n">
+        <v>0</v>
+      </c>
+      <c r="T540" t="inlineStr"/>
+      <c r="U540" t="inlineStr"/>
+      <c r="V540" t="n">
+        <v>0</v>
+      </c>
+      <c r="W540" t="inlineStr"/>
+      <c r="X540" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y540" t="inlineStr"/>
+      <c r="Z540" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA540" t="inlineStr"/>
+      <c r="AB540" t="inlineStr"/>
+      <c r="AC540" t="inlineStr"/>
+      <c r="AD540" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B541" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C541" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>350</v>
+      </c>
+      <c r="F541" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>2301520 000024/2024</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>CONCORRENCIA - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I541" t="n">
+        <v>51</v>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K541" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M541" t="n">
+        <v>80</v>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>66.418.765/0001-54</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="Q541" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="R541" t="n">
+        <v>0</v>
+      </c>
+      <c r="S541" t="n">
+        <v>0</v>
+      </c>
+      <c r="T541" t="inlineStr"/>
+      <c r="U541" t="inlineStr"/>
+      <c r="V541" t="n">
+        <v>0</v>
+      </c>
+      <c r="W541" t="inlineStr"/>
+      <c r="X541" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y541" t="inlineStr"/>
+      <c r="Z541" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="AA541" t="inlineStr"/>
+      <c r="AB541" t="inlineStr"/>
+      <c r="AC541" t="inlineStr"/>
+      <c r="AD541" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B542" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C542" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>352</v>
+      </c>
+      <c r="F542" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>2301520 000015/2026</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I542" t="n">
+        <v>51</v>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K542" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M542" t="n">
+        <v>80</v>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q542" t="n">
+        <v>1686732.44</v>
+      </c>
+      <c r="R542" t="n">
+        <v>0</v>
+      </c>
+      <c r="S542" t="n">
+        <v>0</v>
+      </c>
+      <c r="T542" t="inlineStr"/>
+      <c r="U542" t="inlineStr"/>
+      <c r="V542" t="n">
+        <v>0</v>
+      </c>
+      <c r="W542" t="inlineStr"/>
+      <c r="X542" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y542" t="inlineStr"/>
+      <c r="Z542" t="n">
+        <v>1686732.44</v>
+      </c>
+      <c r="AA542" t="inlineStr"/>
+      <c r="AB542" t="inlineStr"/>
+      <c r="AC542" t="inlineStr"/>
+      <c r="AD542" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B543" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C543" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>353</v>
+      </c>
+      <c r="F543" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>2301520 000024/2025</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>CONCORRENCIA - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I543" t="n">
+        <v>39</v>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>OUTROS SERVICOS DE TERCEIROS - PESSOA JURIDICA</t>
+        </is>
+      </c>
+      <c r="K543" t="n">
+        <v>3951</v>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+        </is>
+      </c>
+      <c r="M543" t="n">
+        <v>80</v>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>34.037.705/0001-03</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
+        </is>
+      </c>
+      <c r="Q543" t="n">
+        <v>818191.17</v>
+      </c>
+      <c r="R543" t="n">
+        <v>0</v>
+      </c>
+      <c r="S543" t="n">
+        <v>0</v>
+      </c>
+      <c r="T543" t="inlineStr"/>
+      <c r="U543" t="inlineStr"/>
+      <c r="V543" t="n">
+        <v>0</v>
+      </c>
+      <c r="W543" t="inlineStr"/>
+      <c r="X543" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y543" t="inlineStr"/>
+      <c r="Z543" t="n">
+        <v>818191.17</v>
+      </c>
+      <c r="AA543" t="inlineStr"/>
+      <c r="AB543" t="inlineStr"/>
+      <c r="AC543" t="inlineStr"/>
+      <c r="AD543" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B544" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C544" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>354</v>
+      </c>
+      <c r="F544" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>2301520 000015/2026</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I544" t="n">
+        <v>51</v>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K544" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M544" t="n">
+        <v>80</v>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q544" t="n">
+        <v>313267.56</v>
+      </c>
+      <c r="R544" t="n">
+        <v>0</v>
+      </c>
+      <c r="S544" t="n">
+        <v>0</v>
+      </c>
+      <c r="T544" t="inlineStr"/>
+      <c r="U544" t="inlineStr"/>
+      <c r="V544" t="n">
+        <v>0</v>
+      </c>
+      <c r="W544" t="inlineStr"/>
+      <c r="X544" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y544" t="inlineStr"/>
+      <c r="Z544" t="n">
+        <v>313267.56</v>
+      </c>
+      <c r="AA544" t="inlineStr"/>
+      <c r="AB544" t="inlineStr"/>
+      <c r="AC544" t="inlineStr"/>
+      <c r="AD544" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B545" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C545" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>355</v>
+      </c>
+      <c r="F545" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>2301520 000015/2026</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I545" t="n">
+        <v>51</v>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K545" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M545" t="n">
+        <v>80</v>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q545" t="n">
+        <v>47429.55</v>
+      </c>
+      <c r="R545" t="n">
+        <v>0</v>
+      </c>
+      <c r="S545" t="n">
+        <v>0</v>
+      </c>
+      <c r="T545" t="inlineStr"/>
+      <c r="U545" t="inlineStr"/>
+      <c r="V545" t="n">
+        <v>0</v>
+      </c>
+      <c r="W545" t="inlineStr"/>
+      <c r="X545" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y545" t="inlineStr"/>
+      <c r="Z545" t="n">
+        <v>47429.55</v>
+      </c>
+      <c r="AA545" t="inlineStr"/>
+      <c r="AB545" t="inlineStr"/>
+      <c r="AC545" t="inlineStr"/>
+      <c r="AD545" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B546" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C546" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>356</v>
+      </c>
+      <c r="F546" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I546" t="n">
+        <v>93</v>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K546" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M546" t="n">
+        <v>80</v>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q546" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R546" t="n">
+        <v>0</v>
+      </c>
+      <c r="S546" t="n">
+        <v>0</v>
+      </c>
+      <c r="T546" t="inlineStr"/>
+      <c r="U546" t="inlineStr"/>
+      <c r="V546" t="n">
+        <v>0</v>
+      </c>
+      <c r="W546" t="inlineStr"/>
+      <c r="X546" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y546" t="inlineStr"/>
+      <c r="Z546" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AA546" t="inlineStr"/>
+      <c r="AB546" t="inlineStr"/>
+      <c r="AC546" t="inlineStr"/>
+      <c r="AD546" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
